--- a/resources/templates/standard/A6100-01.xlsx
+++ b/resources/templates/standard/A6100-01.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="116">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>나의 제안 (갑지)</t>
   </si>
@@ -1280,12 +1283,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1359,7 +1364,7 @@
     </row>
     <row r="3" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1373,7 +1378,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -1387,7 +1392,7 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
@@ -1403,7 +1408,7 @@
     </row>
     <row r="4" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1417,7 +1422,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
       <c r="M4" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -1431,14 +1436,14 @@
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="8"/>
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
       <c r="AD4" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
@@ -1449,7 +1454,7 @@
     </row>
     <row r="5" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1489,7 +1494,7 @@
     </row>
     <row r="6" ht="24.95" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
@@ -1530,7 +1535,7 @@
     <row r="7" ht="24" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
@@ -1549,7 +1554,7 @@
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
       <c r="S7" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -2142,11 +2147,11 @@
     <row r="23" ht="20.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -2156,7 +2161,7 @@
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
@@ -2166,14 +2171,14 @@
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U23" s="19"/>
       <c r="V23" s="19"/>
       <c r="W23" s="19"/>
       <c r="X23" s="16"/>
       <c r="Y23" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z23" s="18"/>
       <c r="AA23" s="18"/>
@@ -2192,25 +2197,25 @@
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
       <c r="D24" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="P24" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
@@ -2221,12 +2226,12 @@
       <c r="W24" s="19"/>
       <c r="X24" s="16"/>
       <c r="Y24" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
       <c r="AB24" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC24" s="7"/>
       <c r="AD24" s="7"/>
@@ -2263,12 +2268,12 @@
       <c r="W25" s="7"/>
       <c r="X25" s="16"/>
       <c r="Y25" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC25" s="7"/>
       <c r="AD25" s="7"/>
@@ -2305,12 +2310,12 @@
       <c r="W26" s="7"/>
       <c r="X26" s="16"/>
       <c r="Y26" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
       <c r="AB26" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC26" s="7"/>
       <c r="AD26" s="7"/>
@@ -2326,43 +2331,43 @@
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
       <c r="P27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q27" s="7"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="16"/>
       <c r="Y27" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
       <c r="AB27" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC27" s="7"/>
       <c r="AD27" s="7"/>
@@ -2399,12 +2404,12 @@
       <c r="W28" s="7"/>
       <c r="X28" s="16"/>
       <c r="Y28" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC28" s="7"/>
       <c r="AD28" s="7"/>
@@ -2441,12 +2446,12 @@
       <c r="W29" s="7"/>
       <c r="X29" s="16"/>
       <c r="Y29" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AC29" s="7"/>
       <c r="AD29" s="7"/>
@@ -2483,12 +2488,12 @@
       <c r="W30" s="16"/>
       <c r="X30" s="16"/>
       <c r="Y30" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
       <c r="AB30" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC30" s="7"/>
       <c r="AD30" s="7"/>
@@ -2543,7 +2548,7 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2656,7 +2661,7 @@
     <row r="35" ht="20.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" s="27"/>
       <c r="D35" s="27"/>
@@ -2696,7 +2701,7 @@
     <row r="36" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36" s="29"/>
       <c r="D36" s="29"/>
@@ -2736,7 +2741,7 @@
     <row r="37" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
@@ -2776,7 +2781,7 @@
     <row r="38" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38" s="30"/>
       <c r="D38" s="30"/>
@@ -2816,7 +2821,7 @@
     <row r="39" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
@@ -2856,7 +2861,7 @@
     <row r="40" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
@@ -2896,7 +2901,7 @@
     <row r="41" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
@@ -2936,7 +2941,7 @@
     <row r="42" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C42" s="29"/>
       <c r="D42" s="29"/>
@@ -2976,7 +2981,7 @@
     <row r="43" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C43" s="29"/>
       <c r="D43" s="29"/>
@@ -3016,7 +3021,7 @@
     <row r="44" ht="20.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
       <c r="B44" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
@@ -3056,7 +3061,7 @@
     <row r="45" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="32"/>
       <c r="D45" s="32"/>
@@ -3096,14 +3101,14 @@
     <row r="46" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
       <c r="B46" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C46" s="35"/>
       <c r="D46" s="35"/>
       <c r="E46" s="35"/>
       <c r="F46" s="35"/>
       <c r="G46" s="36" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H46" s="36"/>
       <c r="I46" s="36"/>
@@ -3129,7 +3134,7 @@
       <c r="AC46" s="36"/>
       <c r="AD46" s="36"/>
       <c r="AE46" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AF46" s="37"/>
       <c r="AG46" s="37"/>
@@ -3140,56 +3145,56 @@
     <row r="47" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="39"/>
       <c r="B47" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D47" s="41"/>
       <c r="E47" s="41"/>
       <c r="F47" s="41"/>
       <c r="G47" s="42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H47" s="42"/>
       <c r="I47" s="42"/>
       <c r="J47" s="42"/>
       <c r="K47" s="42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L47" s="42"/>
       <c r="M47" s="42"/>
       <c r="N47" s="42"/>
       <c r="O47" s="42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P47" s="42"/>
       <c r="Q47" s="42"/>
       <c r="R47" s="42"/>
       <c r="S47" s="42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T47" s="42"/>
       <c r="U47" s="42"/>
       <c r="V47" s="42"/>
       <c r="W47" s="42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X47" s="42"/>
       <c r="Y47" s="42"/>
       <c r="Z47" s="42"/>
       <c r="AA47" s="42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AB47" s="42"/>
       <c r="AC47" s="42"/>
       <c r="AD47" s="42"/>
       <c r="AE47" s="42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AF47" s="42"/>
       <c r="AG47" s="42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AH47" s="42"/>
       <c r="AI47" s="38"/>
@@ -3199,43 +3204,43 @@
       <c r="A48" s="39"/>
       <c r="B48" s="40"/>
       <c r="C48" s="43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D48" s="43"/>
       <c r="E48" s="43"/>
       <c r="F48" s="43"/>
       <c r="G48" s="44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H48" s="44"/>
       <c r="I48" s="44"/>
       <c r="J48" s="44"/>
       <c r="K48" s="45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="L48" s="45"/>
       <c r="M48" s="45"/>
       <c r="N48" s="45"/>
       <c r="O48" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P48" s="45"/>
       <c r="Q48" s="45"/>
       <c r="R48" s="45"/>
       <c r="S48" s="45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T48" s="45"/>
       <c r="U48" s="45"/>
       <c r="V48" s="45"/>
       <c r="W48" s="45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="X48" s="45"/>
       <c r="Y48" s="45"/>
       <c r="Z48" s="45"/>
       <c r="AA48" s="45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB48" s="45"/>
       <c r="AC48" s="45"/>
@@ -3251,43 +3256,43 @@
       <c r="A49" s="39"/>
       <c r="B49" s="40"/>
       <c r="C49" s="43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D49" s="43"/>
       <c r="E49" s="43"/>
       <c r="F49" s="43"/>
       <c r="G49" s="44" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H49" s="44"/>
       <c r="I49" s="44"/>
       <c r="J49" s="44"/>
       <c r="K49" s="44" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L49" s="44"/>
       <c r="M49" s="44"/>
       <c r="N49" s="44"/>
       <c r="O49" s="44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P49" s="44"/>
       <c r="Q49" s="44"/>
       <c r="R49" s="44"/>
       <c r="S49" s="44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T49" s="44"/>
       <c r="U49" s="44"/>
       <c r="V49" s="44"/>
       <c r="W49" s="44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="X49" s="44"/>
       <c r="Y49" s="44"/>
       <c r="Z49" s="44"/>
       <c r="AA49" s="44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AB49" s="44"/>
       <c r="AC49" s="44"/>
@@ -3303,7 +3308,7 @@
       <c r="A50" s="39"/>
       <c r="B50" s="40"/>
       <c r="C50" s="46" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D50" s="46"/>
       <c r="E50" s="46"/>
@@ -3342,38 +3347,38 @@
     <row r="51" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="39"/>
       <c r="B51" s="47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C51" s="47"/>
       <c r="D51" s="47"/>
       <c r="E51" s="47"/>
       <c r="F51" s="47"/>
       <c r="G51" s="42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H51" s="42"/>
       <c r="I51" s="42"/>
       <c r="J51" s="42"/>
       <c r="K51" s="42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L51" s="42"/>
       <c r="M51" s="42"/>
       <c r="N51" s="42"/>
       <c r="O51" s="42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P51" s="42"/>
       <c r="Q51" s="42"/>
       <c r="R51" s="42"/>
       <c r="S51" s="42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T51" s="42"/>
       <c r="U51" s="42"/>
       <c r="V51" s="42"/>
       <c r="W51" s="42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X51" s="42"/>
       <c r="Y51" s="42"/>
@@ -3397,31 +3402,31 @@
       <c r="E52" s="47"/>
       <c r="F52" s="47"/>
       <c r="G52" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H52" s="44"/>
       <c r="I52" s="44"/>
       <c r="J52" s="44"/>
       <c r="K52" s="44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L52" s="44"/>
       <c r="M52" s="44"/>
       <c r="N52" s="44"/>
       <c r="O52" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P52" s="44"/>
       <c r="Q52" s="44"/>
       <c r="R52" s="44"/>
       <c r="S52" s="44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T52" s="44"/>
       <c r="U52" s="44"/>
       <c r="V52" s="44"/>
       <c r="W52" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X52" s="44"/>
       <c r="Y52" s="44"/>
@@ -3440,38 +3445,38 @@
     <row r="53" ht="36" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="39"/>
       <c r="B53" s="49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C53" s="49"/>
       <c r="D53" s="49"/>
       <c r="E53" s="49"/>
       <c r="F53" s="49"/>
       <c r="G53" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H53" s="50"/>
       <c r="I53" s="50"/>
       <c r="J53" s="50"/>
       <c r="K53" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L53" s="50"/>
       <c r="M53" s="50"/>
       <c r="N53" s="50"/>
       <c r="O53" s="50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P53" s="50"/>
       <c r="Q53" s="50"/>
       <c r="R53" s="50"/>
       <c r="S53" s="50" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T53" s="50"/>
       <c r="U53" s="50"/>
       <c r="V53" s="50"/>
       <c r="W53" s="50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="X53" s="50"/>
       <c r="Y53" s="50"/>
@@ -3490,38 +3495,38 @@
     <row r="54" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="39"/>
       <c r="B54" s="52" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C54" s="52"/>
       <c r="D54" s="52"/>
       <c r="E54" s="52"/>
       <c r="F54" s="52"/>
       <c r="G54" s="53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="53"/>
       <c r="J54" s="53"/>
       <c r="K54" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L54" s="53"/>
       <c r="M54" s="53"/>
       <c r="N54" s="53"/>
       <c r="O54" s="53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P54" s="53"/>
       <c r="Q54" s="53"/>
       <c r="R54" s="53"/>
       <c r="S54" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T54" s="53"/>
       <c r="U54" s="53"/>
       <c r="V54" s="53"/>
       <c r="W54" s="53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X54" s="53"/>
       <c r="Y54" s="53"/>
@@ -3545,31 +3550,31 @@
       <c r="E55" s="52"/>
       <c r="F55" s="52"/>
       <c r="G55" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" s="44"/>
       <c r="I55" s="44"/>
       <c r="J55" s="44"/>
       <c r="K55" s="44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L55" s="44"/>
       <c r="M55" s="44"/>
       <c r="N55" s="44"/>
       <c r="O55" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P55" s="44"/>
       <c r="Q55" s="44"/>
       <c r="R55" s="44"/>
       <c r="S55" s="44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T55" s="44"/>
       <c r="U55" s="44"/>
       <c r="V55" s="44"/>
       <c r="W55" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X55" s="44"/>
       <c r="Y55" s="44"/>
@@ -3588,38 +3593,38 @@
     <row r="56" ht="36" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="39"/>
       <c r="B56" s="55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C56" s="55"/>
       <c r="D56" s="55"/>
       <c r="E56" s="55"/>
       <c r="F56" s="55"/>
       <c r="G56" s="56" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H56" s="56"/>
       <c r="I56" s="56"/>
       <c r="J56" s="56"/>
       <c r="K56" s="57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L56" s="57"/>
       <c r="M56" s="57"/>
       <c r="N56" s="57"/>
       <c r="O56" s="57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P56" s="57"/>
       <c r="Q56" s="57"/>
       <c r="R56" s="57"/>
       <c r="S56" s="57" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T56" s="57"/>
       <c r="U56" s="57"/>
       <c r="V56" s="57"/>
       <c r="W56" s="57" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="X56" s="57"/>
       <c r="Y56" s="57"/>
@@ -3638,38 +3643,38 @@
     <row r="57" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="39"/>
       <c r="B57" s="59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C57" s="59"/>
       <c r="D57" s="59"/>
       <c r="E57" s="59"/>
       <c r="F57" s="59"/>
       <c r="G57" s="53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H57" s="53"/>
       <c r="I57" s="53"/>
       <c r="J57" s="53"/>
       <c r="K57" s="53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L57" s="53"/>
       <c r="M57" s="53"/>
       <c r="N57" s="53"/>
       <c r="O57" s="53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P57" s="53"/>
       <c r="Q57" s="53"/>
       <c r="R57" s="53"/>
       <c r="S57" s="53" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T57" s="53"/>
       <c r="U57" s="53"/>
       <c r="V57" s="53"/>
       <c r="W57" s="53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X57" s="53"/>
       <c r="Y57" s="53"/>
@@ -3693,31 +3698,31 @@
       <c r="E58" s="59"/>
       <c r="F58" s="59"/>
       <c r="G58" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H58" s="44"/>
       <c r="I58" s="44"/>
       <c r="J58" s="44"/>
       <c r="K58" s="44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L58" s="44"/>
       <c r="M58" s="44"/>
       <c r="N58" s="44"/>
       <c r="O58" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P58" s="44"/>
       <c r="Q58" s="44"/>
       <c r="R58" s="44"/>
       <c r="S58" s="44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T58" s="44"/>
       <c r="U58" s="44"/>
       <c r="V58" s="44"/>
       <c r="W58" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X58" s="44"/>
       <c r="Y58" s="44"/>
@@ -3736,38 +3741,38 @@
     <row r="59" ht="36" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" s="39"/>
       <c r="B59" s="49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C59" s="49"/>
       <c r="D59" s="49"/>
       <c r="E59" s="49"/>
       <c r="F59" s="49"/>
       <c r="G59" s="50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H59" s="50"/>
       <c r="I59" s="50"/>
       <c r="J59" s="50"/>
       <c r="K59" s="50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L59" s="50"/>
       <c r="M59" s="50"/>
       <c r="N59" s="50"/>
       <c r="O59" s="50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P59" s="50"/>
       <c r="Q59" s="50"/>
       <c r="R59" s="50"/>
       <c r="S59" s="50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T59" s="50"/>
       <c r="U59" s="50"/>
       <c r="V59" s="50"/>
       <c r="W59" s="61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="X59" s="61"/>
       <c r="Y59" s="61"/>
@@ -3786,38 +3791,38 @@
     <row r="60" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" s="39"/>
       <c r="B60" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="52"/>
       <c r="D60" s="52"/>
       <c r="E60" s="52"/>
       <c r="F60" s="52"/>
       <c r="G60" s="53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H60" s="53"/>
       <c r="I60" s="53"/>
       <c r="J60" s="53"/>
       <c r="K60" s="53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L60" s="53"/>
       <c r="M60" s="53"/>
       <c r="N60" s="53"/>
       <c r="O60" s="53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P60" s="53"/>
       <c r="Q60" s="53"/>
       <c r="R60" s="53"/>
       <c r="S60" s="53" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T60" s="53"/>
       <c r="U60" s="53"/>
       <c r="V60" s="53"/>
       <c r="W60" s="53" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="X60" s="53"/>
       <c r="Y60" s="53"/>
@@ -3841,31 +3846,31 @@
       <c r="E61" s="52"/>
       <c r="F61" s="52"/>
       <c r="G61" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H61" s="44"/>
       <c r="I61" s="44"/>
       <c r="J61" s="44"/>
       <c r="K61" s="44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L61" s="44"/>
       <c r="M61" s="44"/>
       <c r="N61" s="44"/>
       <c r="O61" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P61" s="44"/>
       <c r="Q61" s="44"/>
       <c r="R61" s="44"/>
       <c r="S61" s="44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T61" s="44"/>
       <c r="U61" s="44"/>
       <c r="V61" s="44"/>
       <c r="W61" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="X61" s="44"/>
       <c r="Y61" s="44"/>
@@ -3884,14 +3889,14 @@
     <row r="62" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" s="39"/>
       <c r="B62" s="62" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C62" s="62"/>
       <c r="D62" s="62"/>
       <c r="E62" s="62"/>
       <c r="F62" s="62"/>
       <c r="G62" s="63" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H62" s="63"/>
       <c r="I62" s="63"/>
@@ -3926,7 +3931,7 @@
     <row r="63" ht="15" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" s="39"/>
       <c r="B63" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C63" s="64"/>
       <c r="D63" s="64"/>
@@ -3966,7 +3971,7 @@
     <row r="64" ht="20.1" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" s="12"/>
       <c r="B64" s="66" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C64" s="66"/>
       <c r="D64" s="66"/>
